--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92559886348</v>
+        <v>46157.93063485159</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93063485159</v>
+        <v>46157.93147052212</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93147052212</v>
+        <v>46157.93391638991</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93391638991</v>
+        <v>46157.93704500532</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93704500532</v>
+        <v>46158.28208872714</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28208872714</v>
+        <v>46158.29662574442</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29662574442</v>
+        <v>46158.29800802418</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29800802418</v>
+        <v>46158.33377990617</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33377990617</v>
+        <v>46158.36844515456</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Оборотки за 2024 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36844515456</v>
+        <v>46158.3727977881</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
